--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N25_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>24.00545608306032</v>
       </c>
       <c r="E2" t="n">
-        <v>8.871874727783586</v>
+        <v>9.167797751379302</v>
       </c>
       <c r="F2" t="n">
-        <v>8.883718714262429</v>
+        <v>8.946549078232424</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>23.06612185562226</v>
       </c>
       <c r="E3" t="n">
-        <v>8.871874727783586</v>
+        <v>9.167797751379302</v>
       </c>
       <c r="F3" t="n">
-        <v>8.883718714262429</v>
+        <v>8.946549078232424</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>30.31163753371787</v>
       </c>
       <c r="E4" t="n">
-        <v>8.871874727783586</v>
+        <v>9.167797751379302</v>
       </c>
       <c r="F4" t="n">
-        <v>8.883718714262429</v>
+        <v>8.946549078232424</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,23 +576,87 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
+        <v>5.624167706623756</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.683865153421329</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.167797751379302</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.946549078232424</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>W0029F0002T0006Z000C1N25.png</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19.94179536989012</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.74966332645028</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9.167797751379302</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.946549078232424</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>W0029F0002T0006Z000C1N25.png</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
         <v>6.231425824462145</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>6.313386160520015</v>
       </c>
-      <c r="E5" t="n">
-        <v>8.871874727783586</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8.883718714262429</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="E7" t="n">
+        <v>9.167797751379302</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.946549078232424</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>T7604</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.96687954214661</v>
+        <v>3.894617925598825</v>
       </c>
       <c r="D2" t="n">
-        <v>24.00545608306032</v>
+        <v>3.900886613497303</v>
       </c>
       <c r="E2" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F2" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.09059978773912</v>
+        <v>3.752222465507608</v>
       </c>
       <c r="D3" t="n">
-        <v>23.06612185562226</v>
+        <v>3.748244801538617</v>
       </c>
       <c r="E3" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F3" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.145321467953</v>
+        <v>4.898614738542363</v>
       </c>
       <c r="D4" t="n">
-        <v>30.31163753371787</v>
+        <v>4.925641099229153</v>
       </c>
       <c r="E4" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F4" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.624167706623756</v>
+        <v>0.9139272523263604</v>
       </c>
       <c r="D5" t="n">
-        <v>6.683865153421329</v>
+        <v>1.086128087430966</v>
       </c>
       <c r="E5" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F5" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.94179536989012</v>
+        <v>3.240541747607144</v>
       </c>
       <c r="D6" t="n">
-        <v>19.74966332645028</v>
+        <v>3.209320290548171</v>
       </c>
       <c r="E6" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F6" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.231425824462145</v>
+        <v>1.012606696475099</v>
       </c>
       <c r="D7" t="n">
-        <v>6.313386160520015</v>
+        <v>1.025925251084502</v>
       </c>
       <c r="E7" t="n">
-        <v>9.167797751379302</v>
+        <v>1.489767134599137</v>
       </c>
       <c r="F7" t="n">
-        <v>8.946549078232424</v>
+        <v>1.453814225212769</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
